--- a/dati_thevenin_gen.xlsx
+++ b/dati_thevenin_gen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\Università\Lab. Fisica 2\Esperienze\2° Esperienza\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0E9141-8E43-4FBD-84B3-632BE7DE60A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6959CBDB-F039-463B-9378-753E2086AA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="348" yWindow="2052" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,6 +54,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -83,8 +86,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -383,151 +388,151 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>9.31</v>
       </c>
       <c r="C2">
         <v>0.3</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <f>(B2/100)*0.5+0.02</f>
         <v>6.6549999999999998E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>6</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>9.1</v>
       </c>
       <c r="C3">
         <v>0.3</v>
       </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D14" si="0">(B3/100)*0.5+0.02</f>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D11" si="0">(B3/100)*0.5+0.02</f>
         <v>6.5500000000000003E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>8.7200000000000006</v>
       </c>
       <c r="C4">
         <v>0.3</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <f t="shared" si="0"/>
         <v>6.3600000000000004E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>10</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>8.6</v>
       </c>
       <c r="C5">
         <v>0.3</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <f t="shared" si="0"/>
         <v>6.3E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>10.5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>8.42</v>
       </c>
       <c r="C6">
         <v>0.3</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <f t="shared" si="0"/>
         <v>6.2100000000000002E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>8.2799999999999994</v>
       </c>
       <c r="C7">
         <v>0.3</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <f t="shared" si="0"/>
         <v>6.1399999999999996E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>13</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>8.06</v>
       </c>
       <c r="C8">
         <v>0.3</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <f t="shared" si="0"/>
         <v>6.0300000000000006E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>15</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>7.77</v>
       </c>
       <c r="C9">
         <v>0.3</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <f t="shared" si="0"/>
         <v>5.885E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>17.5</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>7.38</v>
       </c>
       <c r="C10">
         <v>0.3</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <f t="shared" si="0"/>
         <v>5.6900000000000006E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>19</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>7.13</v>
       </c>
       <c r="C11">
         <v>0.3</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <f t="shared" si="0"/>
         <v>5.5650000000000005E-2</v>
       </c>
